--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/los-rios.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/los-rios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1079694-528-CM25</t>
+          <t>926853-28-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5920.63</v>
+        <v>1284.84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4777-274-CM26</t>
+          <t>1079694-222-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>31045.91</v>
+        <v>2666.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>926853-9-CM26</t>
+          <t>2906-217-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>845.38</v>
+        <v>26632.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3573-50-CM26</t>
+          <t>1079694-528-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,32 +737,28 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>36123.64</v>
+        <v>5920.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1457902-17-CM26</t>
+          <t>4777-274-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -772,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -787,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oficina de Seguimiento </t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -802,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -817,7 +813,255 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
+        <v>31045.91</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>926853-9-CM26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>65.120.506-9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Zona de Bienestar Valdivia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>845.38</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3573-50-CM26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>36123.64</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1457902-17-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>60.501.000-8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oficina de Seguimiento </t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
         <v>2641.09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1723-493-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.200.600-3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>1056.54</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/los-rios.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oficina de Seguimiento </t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1062,6 +1062,67 @@
       </c>
       <c r="M10" s="2" t="n">
         <v>1056.54</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2906-131-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.200.700-k</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>26610.78</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/los-rios.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/los-rios.xlsx
@@ -562,7 +562,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1017,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1082,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1147,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
